--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdosagebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdosagebase.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdosagebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdosagebase.xlsx
@@ -646,7 +646,7 @@
     <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.200250.2.2.20.30</t>
+    <t>http://jami.jp/CodeSystem/MedicationMethodBasicUsage</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -770,7 +770,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コード</t>
   </si>
   <si>
-    <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードurn:oid:1.2.392.200250.2.2.20.40</t>
+    <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードhttp://jami.jp/CodeSystem/MedicationUsage</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS</t>
@@ -785,7 +785,7 @@
     <t>Dosage.method.coding:unitDigit2.system</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.200250.2.2.20.40</t>
+    <t>http://jami.jp/CodeSystem/MedicationMethodDetailUsage</t>
   </si>
   <si>
     <t>Dosage.method.coding:unitDigit2.version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdosagebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdosagebase.xlsx
@@ -259,7 +259,7 @@
     <t>薬の服用方法・服用した方法、または服用すべき方法</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -321,7 +321,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -875,7 +875,7 @@
 </t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
@@ -930,7 +930,7 @@
     <t>期間にわたって被験者に投与される可能性のある治療物質の最大総量。たとえば、24時間で1000mg。 / The maximum total quantity of a therapeutic substance that may be administered to a subject over the period of time.  For example, 1000mg in 24 hours.</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 rat-1:分子と分母の両方が存在するか、両方が存在します。両方が欠席している場合、いくつかの拡張が存在するものとします / Numerator and denominator SHALL both be present, or both are absent. If both are absent, there SHALL be some extension present {(numerator.empty() xor denominator.exists()) and (numerator.exists() or extension.exists())}</t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdosagebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdosagebase.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="303">
   <si>
     <t>Property</t>
   </si>
@@ -442,18 +442,19 @@
 </t>
   </si>
   <si>
-    <t>投与日時</t>
-  </si>
-  <si>
-    <t>複数回発生する可能性のあるイベントの発生について説明します。タイミングスケジュールは、イベントが発生することが予想または要求される時期を指定するために使用され、過去または進行中のイベントの概要を表すためにも使用できます。簡単にするために、タイミングコンポーネントの定義は「将来の」イベントとして表現されますが、そのようなコンポーネントは歴史的または進行中のイベントを説明するためにも使用できます。
-タイミングスケジュールは、イベントが発生したときのイベントおよび/または基準のリストであり、構造化された形式またはコードとして表現できます。イベントと繰り返し仕様の両方が提供される場合、イベントのリストは、繰り返し構造の情報の解釈として理解されるべきです。 / Describes the occurrence of an event that may occur multiple times. Timing schedules are used for specifying when events are expected or requested to occur, and may also be used to represent the summary of a past or ongoing event.  For simplicity, the definitions of Timing components are expressed as 'future' events, but such components can also be used to describe historic or ongoing events.
-A Timing schedule can be a list of events and/or criteria for when the event happens, which can be expressed in a structured form and/or as a code. When both event and a repeating specification are provided, the list of events should be understood as an interpretation of the information in the repeat structure.</t>
+    <t>薬を投与する必要がある場合 / When medication should be administered</t>
+  </si>
+  <si>
+    <t>薬を投与する必要がある場合。 / When medication should be administered.</t>
+  </si>
+  <si>
+    <t>この属性は、Dosage.Textが入力されると予想される間、常に埋め込まれるとは限りません。両方が入力されている場合、Dosage.textはDosage.timingの内容を反映する必要があります。 / This attribute might not always be populated while the Dosage.text is expected to be populated.  If both are populated, then the Dosage.text should reflect the content of the Dosage.timing.</t>
   </si>
   <si>
     <t>患者に薬を与えるためのタイミングスケジュール。このデータ型により、さまざまな式が可能になります。たとえば、「8時間ごと」。"一日に三回";「2011年12月23日から10日間の朝食の1/2の1/2：」;「2013年10月15日、2013年10月17日、2013年11月1日」。時には、総量 /持続時間として表される場合、レートは期間を意味する場合があります（たとえば、500ml / 2時間は2時間の期間を意味します）。ただし、レートが期間（250ml/hour）を意味しない場合、期間にわたって注入を伝えるためにタイミング.repeat.durationが必要です。 / The timing schedule for giving the medication to the patient. This  data type allows many different expressions. For example: "Every 8 hours"; "Three times a day"; "1/2 an hour before breakfast for 10 days from 23-Dec 2011:"; "15 Oct 2013, 17 Oct 2013 and 1 Nov 2013".  Sometimes, a rate can imply duration when expressed as total volume / duration (e.g.  500mL/2 hours implies a duration of 2 hours).  However, when rate doesn't imply duration (e.g. 250mL/hour), then the timing.repeat.duration is needed to convey the infuse over time period.</t>
   </si>
   <si>
-    <t>QSET&lt;TS&gt; (GTS)</t>
+    <t>.effectiveTime</t>
   </si>
   <si>
     <t>Dosage.asNeeded[x]</t>
@@ -859,30 +860,19 @@
 </t>
   </si>
   <si>
-    <t>固定数量（コンパレータなし） / A fixed quantity (no comparator)</t>
-  </si>
-  <si>
-    <t>コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity</t>
-  </si>
-  <si>
-    <t>使用のコンテキストは、これがどのような量であるか、したがってどのようなユニットを使用できるかを頻繁に定義する場合があります。使用のコンテキストは、コンパレータの値を制限する場合もあります。 / The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
+    <t>用量あたりの薬の量 / Amount of medication per dose</t>
+  </si>
+  <si>
+    <t>用量あたりの薬の量。 / Amount of medication per dose.</t>
+  </si>
+  <si>
+    <t>これは、各有効成分の量ではなく、指定された薬の量を指定することに注意してください。各成分の量は、投薬資源で伝えることができます。たとえば、タブレットが375 mgであることを伝えたい場合は、用量が1つの錠剤であることを伝えたい場合は、薬物リソースを使用して、錠剤が375 mgの薬物XYZで構成されていることを文書化できます。あるいは、用量が375 mgの場合、これが錠剤であることを示すために投薬資源を使用するだけでいいかもしれません。例がドーパミンなどのIVであり、400mgのドーパミンが500 mLのIV溶液で混合されたことを伝えたい場合、これはすべて投薬資源で伝えられます。政権が瞬時であることを意図していない場合（レートが存在するか、タイミングに期間があります）、これは、スケジュールで示されるように、期間にわたって管理される合計額を伝えるために指定できます。 500 mlの用量で、これを4時間以上行う必要があることを伝えるタイミングが使用されます。 / Note that this specifies the quantity of the specified medication, not the quantity for each active ingredient(s). Each ingredient amount can be communicated in the Medication resource. For example, if one wants to communicate that a tablet was 375 mg, where the dose was one tablet, you can use the Medication resource to document that the tablet was comprised of 375 mg of drug XYZ. Alternatively if the dose was 375 mg, then you may only need to use the Medication resource to indicate this was a tablet. If the example were an IV such as dopamine and you wanted to communicate that 400mg of dopamine was mixed in 500 ml of some IV solution, then this would all be communicated in the Medication resource. If the administration is not intended to be instantaneous (rate is present or timing has a duration), this can be specified to convey the total amount to be administered over the period of time as indicated by the schedule e.g. 500 ml in dose, with timing used to convey that this should be done over 4 hours.</t>
   </si>
   <si>
     <t>1つの投与イベントで与えられた治療またはその他の物質の量。 / The amount of therapeutic or other substance given at one administration event.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
+    <t>RXO-2, RXE-3</t>
   </si>
   <si>
     <t>Dosage.doseAndRate.rate[x]</t>
@@ -924,17 +914,16 @@
     <t>単位時間当たりの投薬量の上限</t>
   </si>
   <si>
-    <t>比率データタイプは、関係を数量と共通単位を使用して適切に表現できない場合にのみ、2つの数値の関係を表現するために使用する必要があります。分母値が「1」に固定されていることが知られている場合、比率ではなく数量を使用する必要があります。 / The Ratio datatype should only be used to express a relationship of two numbers if the relationship cannot be suitably expressed using a Quantity and a common unit.  Where the denominator value is known to be fixed to "1", Quantity should be used instead of Ratio.</t>
+    <t>これは、上限があるときに投与量の補助として使用することを目的としています。たとえば、「4時間ごとに最大8時間あたり2錠」。 / This is intended for use as an adjunct to the dosage when there is an upper cap.  For example "2 tablets every 4 hours to a maximum of 8/day".</t>
   </si>
   <si>
     <t>期間にわたって被験者に投与される可能性のある治療物質の最大総量。たとえば、24時間で1000mg。 / The maximum total quantity of a therapeutic substance that may be administered to a subject over the period of time.  For example, 1000mg in 24 hours.</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-rat-1:分子と分母の両方が存在するか、両方が存在します。両方が欠席している場合、いくつかの拡張が存在するものとします / Numerator and denominator SHALL both be present, or both are absent. If both are absent, there SHALL be some extension present {(numerator.empty() xor denominator.exists()) and (numerator.exists() or extension.exists())}</t>
-  </si>
-  <si>
-    <t>RTO</t>
+    <t>.maxDoseQuantity</t>
+  </si>
+  <si>
+    <t>RXO-23, RXE-19</t>
   </si>
   <si>
     <t>Dosage.maxDosePerAdministration</t>
@@ -947,10 +936,13 @@
     <t>1回あたりの投薬量の上限</t>
   </si>
   <si>
-    <t>薬剤に関する簡易的な数量と単位を定めている。ValueおよびCodeを必須とし、comparatorは記述不可。単位についてはMERIT9医薬品単位略号の利用を推進している。(**SHOULD**)</t>
+    <t>これは、上限があるときに投与量の補助として使用することを目的としています。たとえば、5〜10分間で1.5 mg/m2（最大2 mg）IVなどの最大量の体積領域に関連する用量に関連する用量は、1.5 mg/m2、最大2 mgのDosequantityになります。 / This is intended for use as an adjunct to the dosage when there is an upper cap.  For example, a body surface area related dose with a maximum amount, such as 1.5 mg/m2 (maximum 2 mg) IV over 5 – 10 minutes would have doseQuantity of 1.5 mg/m2 and maxDosePerAdministration of 2 mg.</t>
   </si>
   <si>
     <t>投与ごとの被験者に投与される可能性のある治療物質の最大総量。 / The maximum total quantity of a therapeutic substance that may be administered to a subject per administration.</t>
+  </si>
+  <si>
+    <t>not supported</t>
   </si>
   <si>
     <t>Dosage.maxDosePerLifetime</t>
@@ -2312,7 +2304,7 @@
         <v>76</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="K10" t="s" s="2">
         <v>137</v>
@@ -2321,13 +2313,13 @@
         <v>138</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>76</v>
@@ -2391,18 +2383,18 @@
         <v>81</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>108</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2425,16 +2417,16 @@
         <v>103</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2484,7 +2476,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2499,18 +2491,18 @@
         <v>81</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2536,16 +2528,16 @@
         <v>124</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>76</v>
@@ -2574,7 +2566,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>76</v>
@@ -2592,7 +2584,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2607,18 +2599,18 @@
         <v>81</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2644,16 +2636,16 @@
         <v>124</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>76</v>
@@ -2682,7 +2674,7 @@
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>76</v>
@@ -2700,7 +2692,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -2715,18 +2707,18 @@
         <v>81</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2752,16 +2744,16 @@
         <v>124</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>76</v>
@@ -2786,13 +2778,13 @@
         <v>76</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>76</v>
@@ -2810,7 +2802,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -2825,18 +2817,18 @@
         <v>81</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2939,10 +2931,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3047,10 +3039,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3073,19 +3065,19 @@
         <v>103</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>76</v>
@@ -3122,7 +3114,7 @@
         <v>76</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
@@ -3132,7 +3124,7 @@
         <v>98</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3147,21 +3139,21 @@
         <v>81</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>76</v>
@@ -3183,19 +3175,19 @@
         <v>103</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>76</v>
@@ -3224,7 +3216,7 @@
       </c>
       <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>76</v>
@@ -3242,7 +3234,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3257,18 +3249,18 @@
         <v>81</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3371,10 +3363,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3479,10 +3471,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3505,26 +3497,26 @@
         <v>103</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>76</v>
@@ -3566,7 +3558,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3581,18 +3573,18 @@
         <v>81</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3618,13 +3610,13 @@
         <v>85</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3674,7 +3666,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3689,18 +3681,18 @@
         <v>81</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3723,17 +3715,17 @@
         <v>103</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>76</v>
@@ -3782,7 +3774,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -3797,18 +3789,18 @@
         <v>81</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3834,14 +3826,14 @@
         <v>85</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>76</v>
@@ -3890,7 +3882,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -3905,18 +3897,18 @@
         <v>81</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3939,19 +3931,19 @@
         <v>103</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4000,7 +3992,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4015,21 +4007,21 @@
         <v>81</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>76</v>
@@ -4051,19 +4043,19 @@
         <v>103</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>76</v>
@@ -4092,7 +4084,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>76</v>
@@ -4110,7 +4102,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4125,18 +4117,18 @@
         <v>81</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4239,10 +4231,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4347,10 +4339,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4373,26 +4365,26 @@
         <v>103</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>76</v>
@@ -4434,7 +4426,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4449,18 +4441,18 @@
         <v>81</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4486,13 +4478,13 @@
         <v>85</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4542,7 +4534,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4557,18 +4549,18 @@
         <v>81</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4591,17 +4583,17 @@
         <v>103</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>76</v>
@@ -4650,7 +4642,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -4665,18 +4657,18 @@
         <v>81</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4702,14 +4694,14 @@
         <v>85</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>76</v>
@@ -4758,7 +4750,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -4773,18 +4765,18 @@
         <v>81</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4807,19 +4799,19 @@
         <v>103</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>76</v>
@@ -4868,7 +4860,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -4883,18 +4875,18 @@
         <v>81</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4978,7 +4970,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -4993,18 +4985,18 @@
         <v>81</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5027,13 +5019,13 @@
         <v>103</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5084,7 +5076,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5102,15 +5094,15 @@
         <v>76</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5213,10 +5205,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5321,10 +5313,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5350,16 +5342,16 @@
         <v>124</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>76</v>
@@ -5388,7 +5380,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>76</v>
@@ -5406,7 +5398,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5424,15 +5416,15 @@
         <v>76</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5452,22 +5444,22 @@
         <v>76</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>76</v>
@@ -5516,7 +5508,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -5525,24 +5517,24 @@
         <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>277</v>
+        <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>280</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5565,19 +5557,19 @@
         <v>103</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>76</v>
@@ -5626,7 +5618,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -5641,18 +5633,18 @@
         <v>81</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5672,22 +5664,22 @@
         <v>76</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>76</v>
@@ -5736,7 +5728,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -5745,24 +5737,24 @@
         <v>84</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>277</v>
+        <v>76</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>294</v>
+        <v>81</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>108</v>
+        <v>293</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5782,22 +5774,22 @@
         <v>76</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>76</v>
@@ -5846,7 +5838,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -5855,24 +5847,24 @@
         <v>84</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>277</v>
+        <v>76</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>278</v>
+        <v>81</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>280</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5892,22 +5884,20 @@
         <v>76</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>76</v>
@@ -5956,7 +5946,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -5965,16 +5955,16 @@
         <v>84</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>277</v>
+        <v>76</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>278</v>
+        <v>81</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>280</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdosagebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdosagebase.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdosagebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdosagebase.xlsx
@@ -1258,17 +1258,17 @@
   <dimension ref="A1:AL43"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.5" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="34.8515625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="21.21875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="38.15234375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="29.87890625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.9609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="68.55078125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1277,24 +1277,24 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="104.59765625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="77.19140625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="89.67578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.17578125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="128.11328125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="45.6171875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="109.8359375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="39.109375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdosagebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdosagebase.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-06-24</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdosagebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdosagebase.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdosagebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdosagebase.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdosagebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdosagebase.xlsx
@@ -545,7 +545,7 @@
     <t>薬が投与される手法を説明するコード化された概念。 / A coded concept describing the technique by which the medicine is administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
   </si>
   <si>
     <t>.doseQuantity</t>
@@ -879,7 +879,7 @@
   </si>
   <si>
     <t>Ratio
-RangeQuantity {SimpleQuantity}</t>
+RangeQuantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
     <t>薬剤の投与量速度</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdosagebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdosagebase.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdosagebase.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdosagebase.xlsx
@@ -511,7 +511,7 @@
     <t>投与経路</t>
   </si>
   <si>
-    <t>投与経路の一般的パターンに全てのターミノロジが適応しているわけではない。情報モデルはCodeableConceptではなく、直接Codingをを使用してテキストやコーディング、翻訳、そしてエレメントと事前条件、事後条件の関係について管理するためにその構造を提示する必要がある。  
+    <t>投与経路の一般的パターンに全てのターミノロジが適応しているわけではない。情報モデルはCodeableConceptではなく、直接`Coding`を使用してテキストや`Coding`、翻訳、そしてエレメントと事前条件、事後条件の関係について管理するためにその構造を提示する必要がある。
 【JP Core仕様】HL7表0162をベースにした投与経路コードを使用することが望ましいが、ローカルコードも使用可能。</t>
   </si>
   <si>
@@ -604,7 +604,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法１桁コードを識別するURI。</t>
   </si>
   <si>
-    <t>コードは臨時で列記したものや、コードのリストからSNOMED CTのように公式に定義されたものまである（HL7 v3 core principle を参照)。FHIR自体ではコーディング規約を定めてはいないし、意味を暗示するために利用されない(SHALL NOT)。一般的に UserSelected = trueの場合には一つのコードシステムが使われる。</t>
+    <t>コードは臨時で列記したものや、コードのリストからSNOMED CTのように公式に定義されたものまである（HL7 v3 core principle を参照)。FHIR自体ではコード化に関する規約を定めてはいないし、意味を暗示するために利用されない(SHALL NOT)。一般的に UserSelected = trueの場合には一つのコードシステムが使われる。</t>
   </si>
   <si>
     <t>他のコードシステムへの変換や代替のコードシステムを使ってエンコードしてもよい。</t>
@@ -841,7 +841,7 @@
     <t>力価区分</t>
   </si>
   <si>
-    <t>投与速度・量の一般的パターンに全てのターミノロジが適応しているわけではない。情報モデルはCodeableConceptではなく、直接Codingをを使用してテキストやコーディング、翻訳、そしてエレメントと事前条件、事後条件の関係について管理するためにその構造を提示する必要がある。</t>
+    <t>投与速度・量の一般的パターンに全てのターミノロジが適応しているわけではない。情報モデルはCodeableConceptではなく、直接`Coding`を使用してテキストや`Coding`、翻訳、そしてエレメントと事前条件、事後条件の関係について管理するためにその構造を提示する必要がある。</t>
   </si>
   <si>
     <t>このtypeに値が指定されていなければ、"ordered"であることが想定される。</t>
